--- a/Additional Stats/Summary Rough.xlsx
+++ b/Additional Stats/Summary Rough.xlsx
@@ -8,16 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ibrahimkhalil/WorkSpace/Projects &amp; Work/UHI-Study-Savar-Bangladesh/Additional Stats/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4A8CE22-7881-9141-9FCB-6CB64120BAA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC4E2171-565A-5341-A486-896435FC503D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="580" windowWidth="25600" windowHeight="16060" activeTab="1" xr2:uid="{6A2D78C0-AB4A-314A-9704-81EB8958995C}"/>
+    <workbookView xWindow="80" yWindow="580" windowWidth="25520" windowHeight="14800" xr2:uid="{6A2D78C0-AB4A-314A-9704-81EB8958995C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Summary Rough" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="61">
   <si>
     <t>Contents</t>
   </si>
@@ -203,13 +202,58 @@
   </si>
   <si>
     <t>Column2</t>
+  </si>
+  <si>
+    <t>Year Block</t>
+  </si>
+  <si>
+    <t>Satellite Image</t>
+  </si>
+  <si>
+    <t>Landsat 7 ETM+</t>
+  </si>
+  <si>
+    <t>Landsat 8 OLI/TIRS</t>
+  </si>
+  <si>
+    <t>Landsat 9 OLI-2/TIRS-2</t>
+  </si>
+  <si>
+    <t>2024–2025</t>
+  </si>
+  <si>
+    <t>2020–2021</t>
+  </si>
+  <si>
+    <t>2015–2016</t>
+  </si>
+  <si>
+    <t>2010–2011</t>
+  </si>
+  <si>
+    <t>2005–2006</t>
+  </si>
+  <si>
+    <t>2000–2001</t>
+  </si>
+  <si>
+    <t>Landsat 5 TM 
+(Landsat 7 ETM+ SLC-off)</t>
+  </si>
+  <si>
+    <t>Landsat 5 TM
+(Landsat 7 ETM+ SLC-off)</t>
+  </si>
+  <si>
+    <t>Total Scene Taken
+(quality-controlled pixels, at least 50 to 100%)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -312,6 +356,18 @@
     <font>
       <b/>
       <sz val="14"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -432,7 +488,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -466,18 +522,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -514,48 +558,51 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="50">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <color auto="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+  <dxfs count="53">
+    <dxf>
+      <font>
+        <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -565,28 +612,48 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <color auto="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1256,6 +1323,78 @@
     </dxf>
     <dxf>
       <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
         <i val="0"/>
         <strike val="0"/>
@@ -1290,6 +1429,25 @@
         <family val="1"/>
         <scheme val="none"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1351,6 +1509,43 @@
         <family val="1"/>
         <scheme val="none"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1394,6 +1589,43 @@
         <family val="1"/>
         <scheme val="none"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1437,6 +1669,43 @@
         <family val="1"/>
         <scheme val="none"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1480,197 +1749,49 @@
         <family val="1"/>
         <scheme val="none"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor theme="0" tint="-0.14999847407452621"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -1816,55 +1937,67 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{9B9C56A0-2B63-B644-A284-8786B1471E20}" name="Table2" displayName="Table2" ref="A1:M17" headerRowCount="0" totalsRowShown="0" headerRowDxfId="49" dataDxfId="48">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{9B9C56A0-2B63-B644-A284-8786B1471E20}" name="Table2" displayName="Table2" ref="A1:M17" headerRowCount="0" totalsRowShown="0" headerRowDxfId="52" dataDxfId="51">
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{39081AB7-F3EE-454C-8220-069BB2B0314F}" name="Column1" headerRowDxfId="47" dataDxfId="46"/>
-    <tableColumn id="2" xr3:uid="{25A03914-24C7-CB4A-9FA6-00EEFA50E773}" name="Column2" headerRowDxfId="45" dataDxfId="44"/>
-    <tableColumn id="10" xr3:uid="{C8F3974C-BAB2-1D4F-989F-16877C6C9E36}" name="Column9" headerRowDxfId="33" dataDxfId="32"/>
-    <tableColumn id="4" xr3:uid="{7D6642AE-7E1F-984E-9D89-8E1EAFC8180D}" name="Column4" headerRowDxfId="43" dataDxfId="42"/>
-    <tableColumn id="13" xr3:uid="{D71CA205-36BE-D548-9FBB-1CCD4E9BA4CE}" name="Column11" headerRowDxfId="31" dataDxfId="30"/>
-    <tableColumn id="5" xr3:uid="{BA6D5C61-DFBF-4E4C-B31E-6C498FCAD1EC}" name="Column5" headerRowDxfId="41" dataDxfId="40"/>
-    <tableColumn id="14" xr3:uid="{A528D6C9-F074-554D-891F-78EAA7CDF1FB}" name="Column12" headerRowDxfId="29" dataDxfId="28"/>
-    <tableColumn id="6" xr3:uid="{A3B31882-4F1A-0942-BD63-9E340D461EAE}" name="Column6" headerRowDxfId="39" dataDxfId="38"/>
-    <tableColumn id="15" xr3:uid="{1C1532CF-DF2C-9245-BC61-CB5BD6963C76}" name="Column13" headerRowDxfId="27" dataDxfId="26"/>
-    <tableColumn id="7" xr3:uid="{EC885D4C-4D64-9946-B7A5-1483FD184B24}" name="Column7" headerRowDxfId="37" dataDxfId="36"/>
-    <tableColumn id="16" xr3:uid="{575516F0-39FD-1247-A475-AC8201F970A7}" name="Column14" headerRowDxfId="25" dataDxfId="24"/>
-    <tableColumn id="8" xr3:uid="{D2559D1F-C516-304F-BE61-45A4258396A1}" name="Column8" headerRowDxfId="35" dataDxfId="34"/>
-    <tableColumn id="17" xr3:uid="{4E2FEBA8-F3A2-6549-B1ED-C29BF41AADAC}" name="Column15" headerRowDxfId="22" dataDxfId="23"/>
+    <tableColumn id="1" xr3:uid="{39081AB7-F3EE-454C-8220-069BB2B0314F}" name="Column1" headerRowDxfId="50" dataDxfId="49"/>
+    <tableColumn id="2" xr3:uid="{25A03914-24C7-CB4A-9FA6-00EEFA50E773}" name="Column2" headerRowDxfId="48" dataDxfId="47"/>
+    <tableColumn id="10" xr3:uid="{C8F3974C-BAB2-1D4F-989F-16877C6C9E36}" name="Column9" headerRowDxfId="46" dataDxfId="45"/>
+    <tableColumn id="4" xr3:uid="{7D6642AE-7E1F-984E-9D89-8E1EAFC8180D}" name="Column4" headerRowDxfId="44" dataDxfId="43"/>
+    <tableColumn id="13" xr3:uid="{D71CA205-36BE-D548-9FBB-1CCD4E9BA4CE}" name="Column11" headerRowDxfId="42" dataDxfId="41"/>
+    <tableColumn id="5" xr3:uid="{BA6D5C61-DFBF-4E4C-B31E-6C498FCAD1EC}" name="Column5" headerRowDxfId="40" dataDxfId="39"/>
+    <tableColumn id="14" xr3:uid="{A528D6C9-F074-554D-891F-78EAA7CDF1FB}" name="Column12" headerRowDxfId="38" dataDxfId="37"/>
+    <tableColumn id="6" xr3:uid="{A3B31882-4F1A-0942-BD63-9E340D461EAE}" name="Column6" headerRowDxfId="36" dataDxfId="35"/>
+    <tableColumn id="15" xr3:uid="{1C1532CF-DF2C-9245-BC61-CB5BD6963C76}" name="Column13" headerRowDxfId="34" dataDxfId="33"/>
+    <tableColumn id="7" xr3:uid="{EC885D4C-4D64-9946-B7A5-1483FD184B24}" name="Column7" headerRowDxfId="32" dataDxfId="31"/>
+    <tableColumn id="16" xr3:uid="{575516F0-39FD-1247-A475-AC8201F970A7}" name="Column14" headerRowDxfId="30" dataDxfId="29"/>
+    <tableColumn id="8" xr3:uid="{D2559D1F-C516-304F-BE61-45A4258396A1}" name="Column8" headerRowDxfId="28" dataDxfId="27"/>
+    <tableColumn id="17" xr3:uid="{4E2FEBA8-F3A2-6549-B1ED-C29BF41AADAC}" name="Column15" headerRowDxfId="26" dataDxfId="25"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1A33A9EE-5EFC-8648-AA42-E882795C16B6}" name="Table1" displayName="Table1" ref="A41:H52" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11" tableBorderDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1A33A9EE-5EFC-8648-AA42-E882795C16B6}" name="Table1" displayName="Table1" ref="A41:H52" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23" tableBorderDxfId="22">
   <autoFilter ref="A41:H52" xr:uid="{1A33A9EE-5EFC-8648-AA42-E882795C16B6}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{97122A95-0147-7645-90DE-E1ED96458E94}" name="Column1" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{9C8FEDDF-C911-5949-8CE7-37EA18CD0D5F}" name="2000/2001_x000a_(Landsat 7)_x000a_p75" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{92B0E927-165A-C140-9D0A-BBFA7C36D2CF}" name="2005/2006 _x000a_(Landsat 5)_x000a_p75" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{720D8D06-8E74-BA43-8CE2-F78246557A2A}" name="2010/2011 _x000a_(Landsat 5)_x000a_p75" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{43A06E4E-E775-624E-ADF6-6F53FE3F4079}" name="2015/2016 _x000a_(Landsat 8)_x000a_p75" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{DA2599AC-ED2C-E545-87C7-59AA59475AE2}" name="2020/2021_x000a_ (Landsat 8)_x000a_p75" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{B4DE6510-490F-0D4C-B5B1-14925699917E}" name="2024/2025 _x000a_(Landsat 8/9)_x000a_p75" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{3BA65EA5-4A98-2040-AB5C-160799E438D6}" name="Column2" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{97122A95-0147-7645-90DE-E1ED96458E94}" name="Column1" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{9C8FEDDF-C911-5949-8CE7-37EA18CD0D5F}" name="2000/2001_x000a_(Landsat 7)_x000a_p75" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{92B0E927-165A-C140-9D0A-BBFA7C36D2CF}" name="2005/2006 _x000a_(Landsat 5)_x000a_p75" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{720D8D06-8E74-BA43-8CE2-F78246557A2A}" name="2010/2011 _x000a_(Landsat 5)_x000a_p75" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{43A06E4E-E775-624E-ADF6-6F53FE3F4079}" name="2015/2016 _x000a_(Landsat 8)_x000a_p75" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{DA2599AC-ED2C-E545-87C7-59AA59475AE2}" name="2020/2021_x000a_ (Landsat 8)_x000a_p75" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{B4DE6510-490F-0D4C-B5B1-14925699917E}" name="2024/2025 _x000a_(Landsat 8/9)_x000a_p75" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{3BA65EA5-4A98-2040-AB5C-160799E438D6}" name="Column2" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3E6A6088-8BD0-C548-A5CE-84C19C6E9D2E}" name="Table14" displayName="Table14" ref="A1:H12" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" tableBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5D5569C4-1E6B-904E-B505-628AE65851D0}" name="Table4" displayName="Table4" ref="G24:I30" totalsRowShown="0">
+  <autoFilter ref="G24:I30" xr:uid="{5D5569C4-1E6B-904E-B505-628AE65851D0}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{120A4038-7FB5-524D-85C9-88F71917A3B1}" name="Year Block" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{68F705F4-C2BA-EC44-B27F-B7F7B6F88487}" name="Satellite Image" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{72EFAE21-7774-BC47-ACCD-7CC888F5CEFE}" name="Total Scene Taken_x000a_(quality-controlled pixels, at least 50 to 100%)" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3E6A6088-8BD0-C548-A5CE-84C19C6E9D2E}" name="Table14" displayName="Table14" ref="A1:H12" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12" tableBorderDxfId="11">
   <autoFilter ref="A1:H12" xr:uid="{3E6A6088-8BD0-C548-A5CE-84C19C6E9D2E}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{E02ABEAD-59BB-2D47-85BB-08629D92B1A0}" name="Column1" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{B7FA5263-9A9D-ED4C-9A48-81043432787C}" name="2000/2001_x000a_(Landsat 7)_x000a_p75" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{7FE27B50-95F1-ED47-9146-09C07E56405E}" name="2005/2006 _x000a_(Landsat 5)_x000a_p75" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{C21C56EE-3579-F042-A7D9-0590C4136ED1}" name="2010/2011 _x000a_(Landsat 5)_x000a_p75" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{8D111601-C26E-D448-AF0E-5944CCFF82A1}" name="2015/2016 _x000a_(Landsat 8)_x000a_p75" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{6D5902F6-B5CB-4C4B-B967-DEF0EFBDF43D}" name="2020/2021_x000a_ (Landsat 8)_x000a_p75" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{F6F6C829-3CA4-E245-9A02-DE81A2864F54}" name="2024/2025 _x000a_(Landsat 8/9)_x000a_p75" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{7BC4D125-0BB2-A24D-B636-27355AFE891C}" name="Column2" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{E02ABEAD-59BB-2D47-85BB-08629D92B1A0}" name="Column1" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{B7FA5263-9A9D-ED4C-9A48-81043432787C}" name="2000/2001_x000a_(Landsat 7)_x000a_p75" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{7FE27B50-95F1-ED47-9146-09C07E56405E}" name="2005/2006 _x000a_(Landsat 5)_x000a_p75" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{C21C56EE-3579-F042-A7D9-0590C4136ED1}" name="2010/2011 _x000a_(Landsat 5)_x000a_p75" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{8D111601-C26E-D448-AF0E-5944CCFF82A1}" name="2015/2016 _x000a_(Landsat 8)_x000a_p75" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{6D5902F6-B5CB-4C4B-B967-DEF0EFBDF43D}" name="2020/2021_x000a_ (Landsat 8)_x000a_p75" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{F6F6C829-3CA4-E245-9A02-DE81A2864F54}" name="2024/2025 _x000a_(Landsat 8/9)_x000a_p75" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{7BC4D125-0BB2-A24D-B636-27355AFE891C}" name="Column2" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2195,10 +2328,10 @@
     <col min="3" max="3" width="14.5" customWidth="1"/>
     <col min="4" max="4" width="11.5" customWidth="1"/>
     <col min="5" max="6" width="12.6640625" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="13.1640625" customWidth="1"/>
-    <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="13.33203125" customWidth="1"/>
+    <col min="7" max="7" width="20.83203125" customWidth="1"/>
+    <col min="8" max="8" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.5" customWidth="1"/>
     <col min="12" max="12" width="14" customWidth="1"/>
     <col min="13" max="13" width="12.83203125" customWidth="1"/>
@@ -2217,575 +2350,575 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
-      <c r="M1" s="16"/>
-    </row>
-    <row r="2" spans="1:13" s="30" customFormat="1" ht="53" customHeight="1">
-      <c r="A2" s="27" t="s">
+      <c r="M1" s="12"/>
+    </row>
+    <row r="2" spans="1:13" s="26" customFormat="1" ht="53" customHeight="1">
+      <c r="A2" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="E2" s="29" t="s">
+      <c r="E2" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="28" t="s">
+      <c r="F2" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="G2" s="28" t="s">
+      <c r="G2" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="H2" s="29" t="s">
+      <c r="H2" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="29" t="s">
+      <c r="I2" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="J2" s="28" t="s">
+      <c r="J2" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="K2" s="28" t="s">
+      <c r="K2" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="L2" s="29" t="s">
+      <c r="L2" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="M2" s="29" t="s">
+      <c r="M2" s="25" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="18">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
-      <c r="M3" s="32"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+      <c r="K3" s="30"/>
+      <c r="L3" s="30"/>
+      <c r="M3" s="28"/>
     </row>
     <row r="4" spans="1:13" ht="18">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18">
+      <c r="B4" s="14"/>
+      <c r="C4" s="14">
         <v>5</v>
       </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19">
+      <c r="D4" s="15"/>
+      <c r="E4" s="15">
         <v>4</v>
       </c>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18">
+      <c r="F4" s="14"/>
+      <c r="G4" s="14">
         <v>6</v>
       </c>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19">
+      <c r="H4" s="15"/>
+      <c r="I4" s="15">
         <v>12</v>
       </c>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18">
+      <c r="J4" s="14"/>
+      <c r="K4" s="14">
         <v>8</v>
       </c>
-      <c r="L4" s="20"/>
-      <c r="M4" s="19">
+      <c r="L4" s="16"/>
+      <c r="M4" s="15">
         <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="18">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="32"/>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
-      <c r="F5" s="32"/>
-      <c r="G5" s="32"/>
-      <c r="H5" s="32"/>
-      <c r="I5" s="32"/>
-      <c r="J5" s="32"/>
-      <c r="K5" s="32"/>
-      <c r="L5" s="32"/>
-      <c r="M5" s="32"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
     </row>
     <row r="6" spans="1:13" ht="18">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="14">
         <v>37.159999999999997</v>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="14">
         <v>42.72</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="15">
         <v>37.479999999999997</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="15">
         <v>40.299999999999997</v>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="14">
         <v>34.18</v>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="14">
         <v>34.76</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="15">
         <v>36.22</v>
       </c>
-      <c r="I6" s="19">
+      <c r="I6" s="15">
         <v>39.159999999999997</v>
       </c>
-      <c r="J6" s="18">
+      <c r="J6" s="14">
         <v>34.44</v>
       </c>
-      <c r="K6" s="18">
+      <c r="K6" s="14">
         <v>36.35</v>
       </c>
-      <c r="L6" s="19">
+      <c r="L6" s="15">
         <v>35.299999999999997</v>
       </c>
-      <c r="M6" s="19">
+      <c r="M6" s="15">
         <v>36.43</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="18">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="23">
+      <c r="B7" s="19">
         <v>41.13</v>
       </c>
-      <c r="C7" s="23">
+      <c r="C7" s="19">
         <v>45.67</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="20">
         <v>39.89</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="20">
         <v>42.27</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="19">
         <v>36.68</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="19">
         <v>36.67</v>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="20">
         <v>39.590000000000003</v>
       </c>
-      <c r="I7" s="24">
+      <c r="I7" s="20">
         <v>43.89</v>
       </c>
-      <c r="J7" s="23">
+      <c r="J7" s="19">
         <v>37.64</v>
       </c>
-      <c r="K7" s="23">
+      <c r="K7" s="19">
         <v>39.619999999999997</v>
       </c>
-      <c r="L7" s="24">
+      <c r="L7" s="20">
         <v>38.85</v>
       </c>
-      <c r="M7" s="24">
+      <c r="M7" s="20">
         <v>40.299999999999997</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="18">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="21">
+      <c r="B8" s="17">
         <v>3.97</v>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="17">
         <v>2.94</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="18">
         <v>2.41</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="18">
         <v>1.97</v>
       </c>
-      <c r="F8" s="21">
+      <c r="F8" s="17">
         <v>2.5</v>
       </c>
-      <c r="G8" s="21">
+      <c r="G8" s="17">
         <v>1.91</v>
       </c>
-      <c r="H8" s="22">
+      <c r="H8" s="18">
         <v>3.36</v>
       </c>
-      <c r="I8" s="22">
+      <c r="I8" s="18">
         <v>4.7300000000000004</v>
       </c>
-      <c r="J8" s="21">
+      <c r="J8" s="17">
         <v>3.19</v>
       </c>
-      <c r="K8" s="21">
+      <c r="K8" s="17">
         <v>3.26</v>
       </c>
-      <c r="L8" s="22">
+      <c r="L8" s="18">
         <v>3.54</v>
       </c>
-      <c r="M8" s="22">
+      <c r="M8" s="18">
         <v>3.87</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="18">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="21">
         <v>9.36</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="21">
         <v>8.6999999999999993</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="22">
         <v>6.94</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="22">
         <v>5.68</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="21">
         <v>6.88</v>
       </c>
-      <c r="G9" s="25">
+      <c r="G9" s="21">
         <v>7.19</v>
       </c>
-      <c r="H9" s="26">
+      <c r="H9" s="22">
         <v>6.06</v>
       </c>
-      <c r="I9" s="26">
+      <c r="I9" s="22">
         <v>8.18</v>
       </c>
-      <c r="J9" s="25">
+      <c r="J9" s="21">
         <v>6.31</v>
       </c>
-      <c r="K9" s="25">
+      <c r="K9" s="21">
         <v>7.18</v>
       </c>
-      <c r="L9" s="26">
+      <c r="L9" s="22">
         <v>5.93</v>
       </c>
-      <c r="M9" s="26">
+      <c r="M9" s="22">
         <v>6.3</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="18">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="14">
         <v>11.11</v>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="14">
         <v>10.74</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="15">
         <v>8.3000000000000007</v>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="15">
         <v>6.68</v>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="14">
         <v>8.3699999999999992</v>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="14">
         <v>8.94</v>
       </c>
-      <c r="H10" s="19">
+      <c r="H10" s="15">
         <v>7.05</v>
       </c>
-      <c r="I10" s="19">
+      <c r="I10" s="15">
         <v>9.31</v>
       </c>
-      <c r="J10" s="18">
+      <c r="J10" s="14">
         <v>7.31</v>
       </c>
-      <c r="K10" s="18">
+      <c r="K10" s="14">
         <v>8.56</v>
       </c>
-      <c r="L10" s="19">
+      <c r="L10" s="15">
         <v>6.81</v>
       </c>
-      <c r="M10" s="19">
+      <c r="M10" s="15">
         <v>7.18</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="18">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="18">
+      <c r="B11" s="14">
         <v>4.3499999999999996</v>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="14">
         <v>5.56</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="15">
         <v>3.34</v>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="15">
         <v>2.96</v>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="14">
         <v>3.44</v>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="14">
         <v>3.76</v>
       </c>
-      <c r="H11" s="19">
+      <c r="H11" s="15">
         <v>2.19</v>
       </c>
-      <c r="I11" s="19">
+      <c r="I11" s="15">
         <v>2.89</v>
       </c>
-      <c r="J11" s="18">
+      <c r="J11" s="14">
         <v>2.44</v>
       </c>
-      <c r="K11" s="18">
+      <c r="K11" s="14">
         <v>2.88</v>
       </c>
-      <c r="L11" s="19">
+      <c r="L11" s="15">
         <v>1.99</v>
       </c>
-      <c r="M11" s="19">
+      <c r="M11" s="15">
         <v>2.06</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="18">
-      <c r="A12" s="31" t="s">
+      <c r="A12" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="32"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="32"/>
-      <c r="K12" s="32"/>
-      <c r="L12" s="32"/>
-      <c r="M12" s="32"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="28"/>
+      <c r="J12" s="28"/>
+      <c r="K12" s="28"/>
+      <c r="L12" s="28"/>
+      <c r="M12" s="28"/>
     </row>
     <row r="13" spans="1:13" ht="18">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="18">
+      <c r="B13" s="14">
         <v>16.32</v>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="14">
         <v>27.24</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="15">
         <v>50.8</v>
       </c>
-      <c r="E13" s="19">
+      <c r="E13" s="15">
         <v>97.78</v>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="14">
         <v>55.68</v>
       </c>
-      <c r="G13" s="18">
+      <c r="G13" s="14">
         <v>96.21</v>
       </c>
-      <c r="H13" s="19">
+      <c r="H13" s="15">
         <v>43.26</v>
       </c>
-      <c r="I13" s="19">
+      <c r="I13" s="15">
         <v>48.89</v>
       </c>
-      <c r="J13" s="18">
+      <c r="J13" s="14">
         <v>90.65</v>
       </c>
-      <c r="K13" s="18">
+      <c r="K13" s="14">
         <v>99.41</v>
       </c>
-      <c r="L13" s="19">
+      <c r="L13" s="15">
         <v>83.74</v>
       </c>
-      <c r="M13" s="19">
+      <c r="M13" s="15">
         <v>83.64</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="18">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="14">
         <v>206.21</v>
       </c>
-      <c r="C14" s="18">
+      <c r="C14" s="14">
         <v>186</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="15">
         <v>204.98</v>
       </c>
-      <c r="E14" s="19">
+      <c r="E14" s="15">
         <v>220.47</v>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="14">
         <v>178.86</v>
       </c>
-      <c r="G14" s="18">
+      <c r="G14" s="14">
         <v>188.9</v>
       </c>
-      <c r="H14" s="19">
+      <c r="H14" s="15">
         <v>216.19</v>
       </c>
-      <c r="I14" s="19">
+      <c r="I14" s="15">
         <v>225.12</v>
       </c>
-      <c r="J14" s="18">
+      <c r="J14" s="14">
         <v>230.29</v>
       </c>
-      <c r="K14" s="18">
+      <c r="K14" s="14">
         <v>236.52</v>
       </c>
-      <c r="L14" s="19">
+      <c r="L14" s="15">
         <v>212.56</v>
       </c>
-      <c r="M14" s="19">
+      <c r="M14" s="15">
         <v>202.63</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="18">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="18">
+      <c r="B15" s="14">
         <v>79.099999999999994</v>
       </c>
-      <c r="C15" s="18">
+      <c r="C15" s="14">
         <v>80.47</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="15">
         <v>53.14</v>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="15">
         <v>29.04</v>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="14">
         <v>88.16</v>
       </c>
-      <c r="G15" s="18">
+      <c r="G15" s="14">
         <v>59.72</v>
       </c>
-      <c r="H15" s="19">
+      <c r="H15" s="15">
         <v>73.87</v>
       </c>
-      <c r="I15" s="19">
+      <c r="I15" s="15">
         <v>71.930000000000007</v>
       </c>
-      <c r="J15" s="18">
+      <c r="J15" s="14">
         <v>34.869999999999997</v>
       </c>
-      <c r="K15" s="18">
+      <c r="K15" s="14">
         <v>23.08</v>
       </c>
-      <c r="L15" s="19">
+      <c r="L15" s="15">
         <v>57.92</v>
       </c>
-      <c r="M15" s="19">
+      <c r="M15" s="15">
         <v>69.650000000000006</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="18">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="18">
+      <c r="B16" s="14">
         <v>49.81</v>
       </c>
-      <c r="C16" s="18">
+      <c r="C16" s="14">
         <v>23.73</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="15">
         <v>51.78</v>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="15">
         <v>36.840000000000003</v>
       </c>
-      <c r="F16" s="18">
+      <c r="F16" s="14">
         <v>33.450000000000003</v>
       </c>
-      <c r="G16" s="18">
+      <c r="G16" s="14">
         <v>26.83</v>
       </c>
-      <c r="H16" s="19">
+      <c r="H16" s="15">
         <v>19.27</v>
       </c>
-      <c r="I16" s="19">
+      <c r="I16" s="15">
         <v>10.92</v>
       </c>
-      <c r="J16" s="18">
+      <c r="J16" s="14">
         <v>11.74</v>
       </c>
-      <c r="K16" s="18">
+      <c r="K16" s="14">
         <v>13.9</v>
       </c>
-      <c r="L16" s="19">
+      <c r="L16" s="15">
         <v>7.62</v>
       </c>
-      <c r="M16" s="19">
+      <c r="M16" s="15">
         <v>7.89</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="18">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="18">
+      <c r="B17" s="14">
         <v>348.21</v>
       </c>
-      <c r="C17" s="18"/>
-      <c r="D17" s="19">
+      <c r="C17" s="14"/>
+      <c r="D17" s="15">
         <v>348.21</v>
       </c>
-      <c r="E17" s="19"/>
-      <c r="F17" s="18">
+      <c r="E17" s="15"/>
+      <c r="F17" s="14">
         <v>348.21</v>
       </c>
-      <c r="G17" s="18"/>
-      <c r="H17" s="19">
+      <c r="G17" s="14"/>
+      <c r="H17" s="15">
         <v>348.21</v>
       </c>
-      <c r="I17" s="19"/>
-      <c r="J17" s="18">
+      <c r="I17" s="15"/>
+      <c r="J17" s="14">
         <v>348.21</v>
       </c>
-      <c r="K17" s="18"/>
-      <c r="L17" s="19">
+      <c r="K17" s="14"/>
+      <c r="L17" s="15">
         <v>348.21</v>
       </c>
-      <c r="M17" s="19"/>
+      <c r="M17" s="15"/>
     </row>
     <row r="22" spans="1:13" ht="23">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
       <c r="E22" s="8"/>
     </row>
     <row r="23" spans="1:13" ht="34" customHeight="1">
@@ -2801,7 +2934,7 @@
       </c>
       <c r="E23" s="10"/>
     </row>
-    <row r="24" spans="1:13" ht="18">
+    <row r="24" spans="1:13" ht="68">
       <c r="A24" s="4" t="s">
         <v>16</v>
       </c>
@@ -2811,6 +2944,15 @@
       <c r="C24" s="5"/>
       <c r="D24" s="6"/>
       <c r="E24" s="6"/>
+      <c r="G24" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H24" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I24" s="47" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="25" spans="1:13" ht="18">
       <c r="A25" s="4"/>
@@ -2820,8 +2962,18 @@
         <v>20</v>
       </c>
       <c r="E25" s="7"/>
-    </row>
-    <row r="26" spans="1:13" ht="18">
+      <c r="G25" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="H25" s="45" t="s">
+        <v>49</v>
+      </c>
+      <c r="I25" s="45">
+        <v>5</v>
+      </c>
+      <c r="J25" s="44"/>
+    </row>
+    <row r="26" spans="1:13" ht="34">
       <c r="A26" s="4" t="s">
         <v>21</v>
       </c>
@@ -2831,8 +2983,18 @@
       <c r="C26" s="5"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
-    </row>
-    <row r="27" spans="1:13" ht="18">
+      <c r="G26" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="H26" s="47" t="s">
+        <v>58</v>
+      </c>
+      <c r="I26" s="45">
+        <v>4</v>
+      </c>
+      <c r="J26" s="44"/>
+    </row>
+    <row r="27" spans="1:13" ht="34">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -2840,6 +3002,16 @@
         <v>22</v>
       </c>
       <c r="E27" s="7"/>
+      <c r="G27" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="H27" s="47" t="s">
+        <v>59</v>
+      </c>
+      <c r="I27" s="45">
+        <v>6</v>
+      </c>
+      <c r="J27" s="44"/>
     </row>
     <row r="28" spans="1:13" ht="18">
       <c r="A28" s="4" t="s">
@@ -2851,6 +3023,16 @@
       <c r="C28" s="5"/>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
+      <c r="G28" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="H28" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="I28" s="45">
+        <v>12</v>
+      </c>
+      <c r="J28" s="44"/>
     </row>
     <row r="29" spans="1:13" ht="18">
       <c r="A29" s="4"/>
@@ -2860,6 +3042,16 @@
         <v>24</v>
       </c>
       <c r="E29" s="7"/>
+      <c r="G29" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="H29" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="I29" s="45">
+        <v>8</v>
+      </c>
+      <c r="J29" s="44"/>
     </row>
     <row r="30" spans="1:13" ht="18">
       <c r="A30" s="4" t="s">
@@ -2871,6 +3063,16 @@
       <c r="C30" s="5"/>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
+      <c r="G30" s="46" t="s">
+        <v>52</v>
+      </c>
+      <c r="H30" s="45" t="s">
+        <v>51</v>
+      </c>
+      <c r="I30" s="45">
+        <v>27</v>
+      </c>
+      <c r="J30" s="44"/>
     </row>
     <row r="31" spans="1:13" ht="18">
       <c r="A31" s="4"/>
@@ -2922,327 +3124,327 @@
       <c r="E35" s="11"/>
     </row>
     <row r="36" spans="1:12" ht="25" customHeight="1">
-      <c r="A36" s="12" t="s">
+      <c r="A36" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
+      <c r="B36" s="41"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="41"/>
       <c r="E36" s="1"/>
     </row>
     <row r="41" spans="1:12" ht="68">
-      <c r="A41" s="35" t="s">
+      <c r="A41" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="B41" s="36" t="s">
+      <c r="B41" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C41" s="36" t="s">
+      <c r="C41" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="D41" s="36" t="s">
+      <c r="D41" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="E41" s="36" t="s">
+      <c r="E41" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="F41" s="36" t="s">
+      <c r="F41" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="G41" s="36" t="s">
+      <c r="G41" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="H41" s="37" t="s">
+      <c r="H41" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="J41" s="28"/>
-      <c r="L41" s="29"/>
+      <c r="J41" s="24"/>
+      <c r="L41" s="25"/>
     </row>
     <row r="42" spans="1:12" ht="18">
-      <c r="A42" s="38" t="s">
+      <c r="A42" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="B42" s="39">
+      <c r="B42" s="35">
         <v>42.72</v>
       </c>
-      <c r="C42" s="39">
+      <c r="C42" s="35">
         <v>40.299999999999997</v>
       </c>
-      <c r="D42" s="39">
+      <c r="D42" s="35">
         <v>34.76</v>
       </c>
-      <c r="E42" s="39">
+      <c r="E42" s="35">
         <v>39.159999999999997</v>
       </c>
-      <c r="F42" s="39">
+      <c r="F42" s="35">
         <v>36.35</v>
       </c>
-      <c r="G42" s="39">
+      <c r="G42" s="35">
         <v>36.43</v>
       </c>
-      <c r="H42" s="40"/>
-      <c r="J42" s="18"/>
-      <c r="L42" s="19"/>
+      <c r="H42" s="36"/>
+      <c r="J42" s="14"/>
+      <c r="L42" s="15"/>
     </row>
     <row r="43" spans="1:12" ht="18">
-      <c r="A43" s="38" t="s">
+      <c r="A43" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="B43" s="39">
+      <c r="B43" s="35">
         <v>45.67</v>
       </c>
-      <c r="C43" s="39">
+      <c r="C43" s="35">
         <v>42.27</v>
       </c>
-      <c r="D43" s="39">
+      <c r="D43" s="35">
         <v>36.67</v>
       </c>
-      <c r="E43" s="39">
+      <c r="E43" s="35">
         <v>43.89</v>
       </c>
-      <c r="F43" s="39">
+      <c r="F43" s="35">
         <v>39.619999999999997</v>
       </c>
-      <c r="G43" s="39">
+      <c r="G43" s="35">
         <v>40.299999999999997</v>
       </c>
-      <c r="H43" s="40"/>
-      <c r="J43" s="23"/>
-      <c r="L43" s="24"/>
+      <c r="H43" s="36"/>
+      <c r="J43" s="19"/>
+      <c r="L43" s="20"/>
     </row>
     <row r="44" spans="1:12" ht="18">
-      <c r="A44" s="38" t="s">
+      <c r="A44" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="B44" s="39">
+      <c r="B44" s="35">
         <v>2.94</v>
       </c>
-      <c r="C44" s="39">
+      <c r="C44" s="35">
         <v>1.97</v>
       </c>
-      <c r="D44" s="39">
+      <c r="D44" s="35">
         <v>1.91</v>
       </c>
-      <c r="E44" s="39">
+      <c r="E44" s="35">
         <v>4.7300000000000004</v>
       </c>
-      <c r="F44" s="39">
+      <c r="F44" s="35">
         <v>3.26</v>
       </c>
-      <c r="G44" s="39">
+      <c r="G44" s="35">
         <v>3.87</v>
       </c>
-      <c r="H44" s="40"/>
-      <c r="J44" s="21"/>
-      <c r="L44" s="22"/>
+      <c r="H44" s="36"/>
+      <c r="J44" s="17"/>
+      <c r="L44" s="18"/>
     </row>
     <row r="45" spans="1:12" ht="18">
-      <c r="A45" s="38" t="s">
+      <c r="A45" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="B45" s="41">
+      <c r="B45" s="37">
         <v>8.6999999999999993</v>
       </c>
-      <c r="C45" s="41">
+      <c r="C45" s="37">
         <v>5.68</v>
       </c>
-      <c r="D45" s="41">
+      <c r="D45" s="37">
         <v>7.19</v>
       </c>
-      <c r="E45" s="41">
+      <c r="E45" s="37">
         <v>8.18</v>
       </c>
-      <c r="F45" s="41">
+      <c r="F45" s="37">
         <v>7.18</v>
       </c>
-      <c r="G45" s="41">
+      <c r="G45" s="37">
         <v>6.3</v>
       </c>
-      <c r="H45" s="42"/>
-      <c r="J45" s="25"/>
-      <c r="L45" s="26"/>
+      <c r="H45" s="38"/>
+      <c r="J45" s="21"/>
+      <c r="L45" s="22"/>
     </row>
     <row r="46" spans="1:12" ht="18">
-      <c r="A46" s="38" t="s">
+      <c r="A46" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="B46" s="39">
+      <c r="B46" s="35">
         <v>10.74</v>
       </c>
-      <c r="C46" s="39">
+      <c r="C46" s="35">
         <v>6.68</v>
       </c>
-      <c r="D46" s="39">
+      <c r="D46" s="35">
         <v>8.94</v>
       </c>
-      <c r="E46" s="39">
+      <c r="E46" s="35">
         <v>9.31</v>
       </c>
-      <c r="F46" s="39">
+      <c r="F46" s="35">
         <v>8.56</v>
       </c>
-      <c r="G46" s="39">
+      <c r="G46" s="35">
         <v>7.18</v>
       </c>
-      <c r="H46" s="40"/>
-      <c r="J46" s="18"/>
-      <c r="L46" s="19"/>
+      <c r="H46" s="36"/>
+      <c r="J46" s="14"/>
+      <c r="L46" s="15"/>
     </row>
     <row r="47" spans="1:12" ht="18">
-      <c r="A47" s="38" t="s">
+      <c r="A47" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="B47" s="39">
+      <c r="B47" s="35">
         <v>5.56</v>
       </c>
-      <c r="C47" s="39">
+      <c r="C47" s="35">
         <v>2.96</v>
       </c>
-      <c r="D47" s="39">
+      <c r="D47" s="35">
         <v>3.76</v>
       </c>
-      <c r="E47" s="39">
+      <c r="E47" s="35">
         <v>2.89</v>
       </c>
-      <c r="F47" s="39">
+      <c r="F47" s="35">
         <v>2.88</v>
       </c>
-      <c r="G47" s="39">
+      <c r="G47" s="35">
         <v>2.06</v>
       </c>
-      <c r="H47" s="40"/>
-      <c r="J47" s="18"/>
-      <c r="L47" s="19"/>
+      <c r="H47" s="36"/>
+      <c r="J47" s="14"/>
+      <c r="L47" s="15"/>
     </row>
     <row r="48" spans="1:12" ht="18">
-      <c r="A48" s="38" t="s">
+      <c r="A48" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="B48" s="39">
+      <c r="B48" s="35">
         <v>27.24</v>
       </c>
-      <c r="C48" s="39">
+      <c r="C48" s="35">
         <v>97.78</v>
       </c>
-      <c r="D48" s="39">
+      <c r="D48" s="35">
         <v>96.21</v>
       </c>
-      <c r="E48" s="39">
+      <c r="E48" s="35">
         <v>48.89</v>
       </c>
-      <c r="F48" s="39">
+      <c r="F48" s="35">
         <v>99.41</v>
       </c>
-      <c r="G48" s="39">
+      <c r="G48" s="35">
         <v>83.64</v>
       </c>
-      <c r="H48" s="40"/>
-      <c r="J48" s="18"/>
-      <c r="L48" s="19"/>
+      <c r="H48" s="36"/>
+      <c r="J48" s="14"/>
+      <c r="L48" s="15"/>
     </row>
     <row r="49" spans="1:12" ht="18">
-      <c r="A49" s="38" t="s">
+      <c r="A49" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="B49" s="39">
+      <c r="B49" s="35">
         <v>186</v>
       </c>
-      <c r="C49" s="39">
+      <c r="C49" s="35">
         <v>220.47</v>
       </c>
-      <c r="D49" s="39">
+      <c r="D49" s="35">
         <v>188.9</v>
       </c>
-      <c r="E49" s="39">
+      <c r="E49" s="35">
         <v>225.12</v>
       </c>
-      <c r="F49" s="39">
+      <c r="F49" s="35">
         <v>236.52</v>
       </c>
-      <c r="G49" s="39">
+      <c r="G49" s="35">
         <v>202.63</v>
       </c>
-      <c r="H49" s="40"/>
-      <c r="J49" s="18"/>
-      <c r="L49" s="19"/>
+      <c r="H49" s="36"/>
+      <c r="J49" s="14"/>
+      <c r="L49" s="15"/>
     </row>
     <row r="50" spans="1:12" ht="18">
-      <c r="A50" s="38" t="s">
+      <c r="A50" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="B50" s="39">
+      <c r="B50" s="35">
         <v>80.47</v>
       </c>
-      <c r="C50" s="39">
+      <c r="C50" s="35">
         <v>29.04</v>
       </c>
-      <c r="D50" s="39">
+      <c r="D50" s="35">
         <v>59.72</v>
       </c>
-      <c r="E50" s="39">
+      <c r="E50" s="35">
         <v>71.930000000000007</v>
       </c>
-      <c r="F50" s="39">
+      <c r="F50" s="35">
         <v>23.08</v>
       </c>
-      <c r="G50" s="39">
+      <c r="G50" s="35">
         <v>69.650000000000006</v>
       </c>
-      <c r="H50" s="40"/>
-      <c r="J50" s="18"/>
-      <c r="L50" s="19"/>
+      <c r="H50" s="36"/>
+      <c r="J50" s="14"/>
+      <c r="L50" s="15"/>
     </row>
     <row r="51" spans="1:12" ht="18">
-      <c r="A51" s="38" t="s">
+      <c r="A51" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="B51" s="39">
+      <c r="B51" s="35">
         <v>23.73</v>
       </c>
-      <c r="C51" s="39">
+      <c r="C51" s="35">
         <v>36.840000000000003</v>
       </c>
-      <c r="D51" s="39">
+      <c r="D51" s="35">
         <v>26.83</v>
       </c>
-      <c r="E51" s="39">
+      <c r="E51" s="35">
         <v>10.92</v>
       </c>
-      <c r="F51" s="39">
+      <c r="F51" s="35">
         <v>13.9</v>
       </c>
-      <c r="G51" s="39">
+      <c r="G51" s="35">
         <v>7.89</v>
       </c>
-      <c r="H51" s="40"/>
-      <c r="J51" s="18"/>
-      <c r="L51" s="19"/>
+      <c r="H51" s="36"/>
+      <c r="J51" s="14"/>
+      <c r="L51" s="15"/>
     </row>
     <row r="52" spans="1:12" ht="18">
-      <c r="A52" s="43" t="s">
+      <c r="A52" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="B52" s="39">
+      <c r="B52" s="35">
         <v>348.21</v>
       </c>
-      <c r="C52" s="39">
+      <c r="C52" s="35">
         <v>348.21</v>
       </c>
-      <c r="D52" s="39">
+      <c r="D52" s="35">
         <v>348.21</v>
       </c>
-      <c r="E52" s="39">
+      <c r="E52" s="35">
         <v>348.21</v>
       </c>
-      <c r="F52" s="39">
+      <c r="F52" s="35">
         <v>348.21</v>
       </c>
-      <c r="G52" s="39">
+      <c r="G52" s="35">
         <v>348.21</v>
       </c>
-      <c r="H52" s="40"/>
-      <c r="J52" s="18"/>
-      <c r="L52" s="19"/>
+      <c r="H52" s="36"/>
+      <c r="J52" s="14"/>
+      <c r="L52" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3250,9 +3452,11 @@
     <mergeCell ref="A22:D22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="2">
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <tableParts count="3">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
@@ -3263,294 +3467,294 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:8" ht="68">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="36" t="s">
+      <c r="B1" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="C1" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="D1" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="36" t="s">
+      <c r="E1" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="36" t="s">
+      <c r="F1" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="G1" s="36" t="s">
+      <c r="G1" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="H1" s="37" t="s">
+      <c r="H1" s="33" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="18">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="39">
+      <c r="B2" s="35">
         <v>42.72</v>
       </c>
-      <c r="C2" s="39">
+      <c r="C2" s="35">
         <v>40.299999999999997</v>
       </c>
-      <c r="D2" s="39">
+      <c r="D2" s="35">
         <v>34.76</v>
       </c>
-      <c r="E2" s="39">
+      <c r="E2" s="35">
         <v>39.159999999999997</v>
       </c>
-      <c r="F2" s="39">
+      <c r="F2" s="35">
         <v>36.35</v>
       </c>
-      <c r="G2" s="39">
+      <c r="G2" s="35">
         <v>36.43</v>
       </c>
-      <c r="H2" s="40"/>
+      <c r="H2" s="36"/>
     </row>
     <row r="3" spans="1:8" ht="18">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="39">
+      <c r="B3" s="35">
         <v>45.67</v>
       </c>
-      <c r="C3" s="39">
+      <c r="C3" s="35">
         <v>42.27</v>
       </c>
-      <c r="D3" s="39">
+      <c r="D3" s="35">
         <v>36.67</v>
       </c>
-      <c r="E3" s="39">
+      <c r="E3" s="35">
         <v>43.89</v>
       </c>
-      <c r="F3" s="39">
+      <c r="F3" s="35">
         <v>39.619999999999997</v>
       </c>
-      <c r="G3" s="39">
+      <c r="G3" s="35">
         <v>40.299999999999997</v>
       </c>
-      <c r="H3" s="40"/>
+      <c r="H3" s="36"/>
     </row>
     <row r="4" spans="1:8" ht="18">
-      <c r="A4" s="38" t="s">
+      <c r="A4" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="39">
+      <c r="B4" s="35">
         <v>2.94</v>
       </c>
-      <c r="C4" s="39">
+      <c r="C4" s="35">
         <v>1.97</v>
       </c>
-      <c r="D4" s="39">
+      <c r="D4" s="35">
         <v>1.91</v>
       </c>
-      <c r="E4" s="39">
+      <c r="E4" s="35">
         <v>4.7300000000000004</v>
       </c>
-      <c r="F4" s="39">
+      <c r="F4" s="35">
         <v>3.26</v>
       </c>
-      <c r="G4" s="39">
+      <c r="G4" s="35">
         <v>3.87</v>
       </c>
-      <c r="H4" s="40"/>
+      <c r="H4" s="36"/>
     </row>
     <row r="5" spans="1:8" ht="18">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="41">
+      <c r="B5" s="37">
         <v>8.6999999999999993</v>
       </c>
-      <c r="C5" s="41">
+      <c r="C5" s="37">
         <v>5.68</v>
       </c>
-      <c r="D5" s="41">
+      <c r="D5" s="37">
         <v>7.19</v>
       </c>
-      <c r="E5" s="41">
+      <c r="E5" s="37">
         <v>8.18</v>
       </c>
-      <c r="F5" s="41">
+      <c r="F5" s="37">
         <v>7.18</v>
       </c>
-      <c r="G5" s="41">
+      <c r="G5" s="37">
         <v>6.3</v>
       </c>
-      <c r="H5" s="42"/>
+      <c r="H5" s="38"/>
     </row>
     <row r="6" spans="1:8" ht="18">
-      <c r="A6" s="38" t="s">
+      <c r="A6" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="39">
+      <c r="B6" s="35">
         <v>10.74</v>
       </c>
-      <c r="C6" s="39">
+      <c r="C6" s="35">
         <v>6.68</v>
       </c>
-      <c r="D6" s="39">
+      <c r="D6" s="35">
         <v>8.94</v>
       </c>
-      <c r="E6" s="39">
+      <c r="E6" s="35">
         <v>9.31</v>
       </c>
-      <c r="F6" s="39">
+      <c r="F6" s="35">
         <v>8.56</v>
       </c>
-      <c r="G6" s="39">
+      <c r="G6" s="35">
         <v>7.18</v>
       </c>
-      <c r="H6" s="40"/>
+      <c r="H6" s="36"/>
     </row>
     <row r="7" spans="1:8" ht="18">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="39">
+      <c r="B7" s="35">
         <v>5.56</v>
       </c>
-      <c r="C7" s="39">
+      <c r="C7" s="35">
         <v>2.96</v>
       </c>
-      <c r="D7" s="39">
+      <c r="D7" s="35">
         <v>3.76</v>
       </c>
-      <c r="E7" s="39">
+      <c r="E7" s="35">
         <v>2.89</v>
       </c>
-      <c r="F7" s="39">
+      <c r="F7" s="35">
         <v>2.88</v>
       </c>
-      <c r="G7" s="39">
+      <c r="G7" s="35">
         <v>2.06</v>
       </c>
-      <c r="H7" s="40"/>
+      <c r="H7" s="36"/>
     </row>
     <row r="8" spans="1:8" ht="18">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="39">
+      <c r="B8" s="35">
         <v>27.24</v>
       </c>
-      <c r="C8" s="39">
+      <c r="C8" s="35">
         <v>97.78</v>
       </c>
-      <c r="D8" s="39">
+      <c r="D8" s="35">
         <v>96.21</v>
       </c>
-      <c r="E8" s="39">
+      <c r="E8" s="35">
         <v>48.89</v>
       </c>
-      <c r="F8" s="39">
+      <c r="F8" s="35">
         <v>99.41</v>
       </c>
-      <c r="G8" s="39">
+      <c r="G8" s="35">
         <v>83.64</v>
       </c>
-      <c r="H8" s="40"/>
+      <c r="H8" s="36"/>
     </row>
     <row r="9" spans="1:8" ht="18">
-      <c r="A9" s="38" t="s">
+      <c r="A9" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="39">
+      <c r="B9" s="35">
         <v>186</v>
       </c>
-      <c r="C9" s="39">
+      <c r="C9" s="35">
         <v>220.47</v>
       </c>
-      <c r="D9" s="39">
+      <c r="D9" s="35">
         <v>188.9</v>
       </c>
-      <c r="E9" s="39">
+      <c r="E9" s="35">
         <v>225.12</v>
       </c>
-      <c r="F9" s="39">
+      <c r="F9" s="35">
         <v>236.52</v>
       </c>
-      <c r="G9" s="39">
+      <c r="G9" s="35">
         <v>202.63</v>
       </c>
-      <c r="H9" s="40"/>
+      <c r="H9" s="36"/>
     </row>
     <row r="10" spans="1:8" ht="18">
-      <c r="A10" s="38" t="s">
+      <c r="A10" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="39">
+      <c r="B10" s="35">
         <v>80.47</v>
       </c>
-      <c r="C10" s="39">
+      <c r="C10" s="35">
         <v>29.04</v>
       </c>
-      <c r="D10" s="39">
+      <c r="D10" s="35">
         <v>59.72</v>
       </c>
-      <c r="E10" s="39">
+      <c r="E10" s="35">
         <v>71.930000000000007</v>
       </c>
-      <c r="F10" s="39">
+      <c r="F10" s="35">
         <v>23.08</v>
       </c>
-      <c r="G10" s="39">
+      <c r="G10" s="35">
         <v>69.650000000000006</v>
       </c>
-      <c r="H10" s="40"/>
+      <c r="H10" s="36"/>
     </row>
     <row r="11" spans="1:8" ht="18">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="39">
+      <c r="B11" s="35">
         <v>23.73</v>
       </c>
-      <c r="C11" s="39">
+      <c r="C11" s="35">
         <v>36.840000000000003</v>
       </c>
-      <c r="D11" s="39">
+      <c r="D11" s="35">
         <v>26.83</v>
       </c>
-      <c r="E11" s="39">
+      <c r="E11" s="35">
         <v>10.92</v>
       </c>
-      <c r="F11" s="39">
+      <c r="F11" s="35">
         <v>13.9</v>
       </c>
-      <c r="G11" s="39">
+      <c r="G11" s="35">
         <v>7.89</v>
       </c>
-      <c r="H11" s="40"/>
+      <c r="H11" s="36"/>
     </row>
     <row r="12" spans="1:8" ht="18">
-      <c r="A12" s="43" t="s">
+      <c r="A12" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="39">
+      <c r="B12" s="35">
         <v>348.21</v>
       </c>
-      <c r="C12" s="39">
+      <c r="C12" s="35">
         <v>348.21</v>
       </c>
-      <c r="D12" s="39">
+      <c r="D12" s="35">
         <v>348.21</v>
       </c>
-      <c r="E12" s="39">
+      <c r="E12" s="35">
         <v>348.21</v>
       </c>
-      <c r="F12" s="39">
+      <c r="F12" s="35">
         <v>348.21</v>
       </c>
-      <c r="G12" s="39">
+      <c r="G12" s="35">
         <v>348.21</v>
       </c>
-      <c r="H12" s="40"/>
+      <c r="H12" s="36"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
